--- a/artfynd/A 54761-2025 artfynd.xlsx
+++ b/artfynd/A 54761-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13831302</v>
+        <v>88237843</v>
       </c>
       <c r="B2" t="n">
-        <v>60372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101800</v>
+        <v>151</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lamellsnäcka</t>
+          <t>Bronssopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spermodea lamellata</t>
+          <t>Butyriboletus appendiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jeffreys, 1830)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) D.Arora &amp; J.L.Frank</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linnekulla, 400 m S om p.121, Sk</t>
+          <t>Linnekullabäcken, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432451.8682207644</v>
+        <v>432567</v>
       </c>
       <c r="R2" t="n">
-        <v>6197321.225078885</v>
+        <v>6197285</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-07-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bokskog i blockströdd SO-luta. Gles äldre bok, insl. av ek, hassel mm. Gles gulplister, Oxalis mm. I källstråk al mm, här fräken,  Lysim. vulgaris mm, Sphagnum.</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,87 +765,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Se kommentar!</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Göteborgs naturhistoriska museum (GNM)</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>GNM-MF-71473</t>
+          <t>Ädellövskog av bok, avenbok, ek. Skarp rasbrant.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Edelsjö</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik W. Waldén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Markfaunaregistret GNM</t>
-        </is>
-      </c>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88778006</v>
+        <v>88237839</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2979</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Link</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linnekulla, 550 m NO, Sk</t>
+          <t>Linnekullabäcken, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432484.0475773476</v>
+        <v>432579</v>
       </c>
       <c r="R3" t="n">
-        <v>6197475.944856947</v>
+        <v>6197307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,55 +871,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>bokskog med inslag av äldre ek</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88778007</v>
+        <v>88778006</v>
       </c>
       <c r="B4" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432484.0475773476</v>
+        <v>432484</v>
       </c>
       <c r="R4" t="n">
-        <v>6197475.944856947</v>
+        <v>6197476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +963,9 @@
           <t>2020-10-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,62 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100153225</v>
+        <v>13831302</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>101800</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lamellsnäcka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spermodea lamellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Jeffreys, 1830)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linnekullabäcken, Tollarp, Sk</t>
+          <t>Linnekulla, 400 m S om p.121, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432519.071784544</v>
+        <v>432452</v>
       </c>
       <c r="R5" t="n">
-        <v>6197345.392598941</v>
+        <v>6197321</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1117,22 +1057,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1981-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1981-07-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bokskog i blockströdd SO-luta. Gles äldre bok, insl. av ek, hassel mm. Gles gulplister, Oxalis mm. I källstråk al mm, här fräken,  Lysim. vulgaris mm, Sphagnum.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,84 +1076,98 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Se kommentar!</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Göteborgs naturhistoriska museum (GNM)</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>GNM-MF-71473</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Åsbrink</t>
+          <t>Jan Edelsjö</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Åsbrink</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik W. Waldén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Markfaunaregistret GNM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100153216</v>
+        <v>110795228</v>
       </c>
       <c r="B6" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219686</v>
+        <v>102021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linnekullabäcken, Tollarp, Sk</t>
+          <t>Linnekullavägen 188, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432519.071784544</v>
+        <v>432293</v>
       </c>
       <c r="R6" t="n">
-        <v>6197345.392598941</v>
+        <v>6197543</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,22 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,15 +1212,220 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktor Åsbrink</t>
+          <t>Linnea Åsbrink Weissbach</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Åsbrink</t>
+          <t>Linnea Åsbrink Weissbach</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88778007</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Linnekulla, 550 m NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>432484</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6197476</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Vram</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-10-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-10-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88237858</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Linnekullabäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>432534</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6197240</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Vram</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bokskog med inslag av äldre ek. Klibbal längs bäcken.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54761-2025 artfynd.xlsx
+++ b/artfynd/A 54761-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88237843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88237839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88778006</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Markfaunaregistret GNM</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13831302</t>
         </is>
       </c>
     </row>
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110795228</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88778007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,8 +1461,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88237858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>